--- a/data_extactor/batch_10_fa/trimmed/batch_0064_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0064_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | طراحی | ریاضیات | مسکن و ساخت‌وساز | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | طراحی | ریاضیات | ساختمان و ساخت‌وساز | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارشناسان برآورد هزینه و مترورها | مهندسان برق | ممیزان انرژی | مهندسان فروش | مدیران اجرایی و نصب سامانه‌های خورشیدی | مهندسان سامانه‌های انرژی خورشیدی | نصابان سامانه‌های فتوولتائیک خورشیدی</t>
+          <t>کارشناسان برآورد هزینه و مترورها | مهندسان برق | ممیزان انرژی | مهندسان فروش | مدیران اجرای پروژه‌های انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>بازاریابی و فروش | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | حمل‌ونقل و ترابری | رایانه و الکترونیک</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | حمل و نقل | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارشناسان خدمات پس از فروش و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | کارشناسان لجستیک | مدیران خرید و تدارکات | مهندسان فروش | مدیران فروش | کارشناسان فروش عمده و تولیدی محصولات فنی و علمی</t>
+          <t>کارشناسان خدمات و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران خرید و تدارکات | مهندسان فروش | مدیران فروش | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | زبان انگلیسی | صنایع غذایی و تولید خوراک | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | تولید مواد غذایی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | تشخیص گفتار | استدلال قیاسی | دید نزدیک | توجه انتخابی</t>
+          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>صندوق‌داران | کارشناسان خدمات پس از فروش و پشتیبانی مشتریان | بازاریابان حضوری و فروشندگان خیابانی | سرپرستان رده‌اول فروشگاه‌ها و خرده‌فروشی | طراحان چیدمان و دکوراسیون ویترین | فروشندگان خرده‌فروشی | کارشناسان بازاریابی تلفنی</t>
+          <t>صندوق‌داران | کارشناسان خدمات و پشتیبانی مشتریان | بازاریابان حضوری و فروشندگان خیابانی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | طراحان دکوراسیون و ویترین مغازه | فروشندگان خرده‌فروشی | کارشناسان بازاریابی تلفنی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | تفکر انتقادی | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | علوم ارتباطات و رسانه | هنرهای تجسمی و زیبا | زبان انگلیسی | بازاریابی و فروش | طراحی</t>
+          <t>خدمات مشتری و شخصی | ارتباطات و رسانه | هنرهای زیبا | زبان انگلیسی | فروش و بازاریابی | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | هماهنگی کل بدن | تعادل بدنی | دامنه انعطاف‌پذیری بدن</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>حفظ فیگور و ژست در محیط‌های استودیویی | تعامل و هماهنگی نزدیک با گروه تصویربرداری و طراحان | محیط سرپوشیده با تهویهٔ مطبوع | حفظ انضباط فیزیکی و ظاهری در طول جلسات کاری</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بازیگران | مسئولان لباس و تن‌پوش | هنرمندان رقص و حرکات موزون | معرفی‌کنندگان و مروجان کالا | طراحان لباس و مد | چهره‌پردازان و گریمورهای تئاتر و سینما | عکاسان</t>
+          <t>بازیگران | متصدیان و جامه داران لباس صحنه | هنرمندان رقص و حرکات موزون | معرفی‌کنندگان و مروجان کالا | طراحان مد و پوشاک | چهره‌پردازان و گریموران تئاتر و سینما | عکاسان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | درک مطلب | شنیدن فعال | یادگیری فعال | نگارش | نظارت</t>
+          <t>سخن گفتن | تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>بازاریابی و فروش | خدمات مشتریان و خدمات فردی | حقوق و امور دولتی | مدیریت و امور اداری | اقتصاد و حسابداری | مسکن و ساخت‌وساز</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | قانون و دولت | مدیریت و اداره | اقتصاد و حسابداری | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | دید نزدیک | وضوح گفتار | بیان کتبی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | وضوح گفتار | بیان کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ارزیابان و کارشناسان رسمی املاک | مشاوران اعتباری و تسهیلاتی | کارشناسان و مسئولان اعطای وام | مشاوران مالی شخصی | مدیران مجتمع‌های مسکونی، تجاری و املاک | مشاوران و کارشناسان فروش املاک | مدیران فروش</t>
+          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | مشاوران اعتباری و مدیریت بدهی | کارشناسان و مسئولان تسهیلات و اعتبارات | مشاوران مالی فردی | مدیران املاک، مستغلات و مجتمع‌های مسکونی | مشاوران و کارشناسان فروش املاک | مدیران فروش</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | حقوق و امور دولتی | امور اداری و دفتری | مدیریت و امور اداری | مسکن و ساخت‌وساز</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | قانون و دولت | اداری | مدیریت و اداره | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ارزیابان و کارشناسان رسمی املاک | مشاوران اعتباری و تسهیلاتی | کارشناسان و مسئولان اعطای وام | مشاوران مالی شخصی | مدیران مجتمع‌های مسکونی، تجاری و املاک | کارگزاران و مدیران معاملات املاک | مدیران فروش</t>
+          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | مشاوران اعتباری و مدیریت بدهی | کارشناسان و مسئولان تسهیلات و اعتبارات | مشاوران مالی فردی | مدیران املاک، مستغلات و مجتمع‌های مسکونی | کارگزاران و مدیران معاملات املاک | مدیران فروش</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>سخن گفتن | تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | مهندسی و فناوری | ریاضیات | مدیریت و امور اداری | طراحی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مهندسی و فناوری | ریاضیات | مدیریت و اداره | طراحی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>طراحان تجاری و صنعتی | مهندسان برق | مهندسان صنایع | مهندسان مکانیک | کارشناسان فروش خدمات به‌جز تبلیغات، بیمه، مالی و گردشگری | کارشناسان فروش عمده و تولیدی محصولات فنی و علمی | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی</t>
+          <t>طراحان تجاری و صنعتی | مهندسان برق | مهندسان صنایع | مهندسان مکانیک | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>بازاریابی و فروش | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک | علوم ارتباطات و رسانه</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارگزاران فروش تبلیغات | کارشناسان خدمات پس از فروش و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | بازاریابان حضوری و فروشندگان خیابانی | کارمندان ثبت و پیگیری سفارش‌ها | فروشندگان خرده‌فروشی | اپراتورهای تلفن‌خانه و مراکز پاسخ‌گویی</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | کارشناسان خدمات و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | بازاریابان حضوری و فروشندگان خیابانی | متصدیان ثبت و پیگیری سفارش‌ها | فروشندگان خرده‌فروشی | اپراتورهای مراکز تلفن و پاسخگویی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,22 +959,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزارهای مسیریابی و نقشه‌خوانی | نرم‌افزار مدیریت فایل‌ها در گوشی هوشمند | نرم‌افزار مرورگر وب | Microsoft Excel | شبکه‌های اجتماعی</t>
+          <t>Facebook | نرم‌افزار مدیریت فایل‌ها در گوشی هوشمند | نرم‌افزار Microsoft Office | نرم‌افزار نقشه‌برداری مسیر | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | زبان انگلیسی | امور اداری و دفتری | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | اداری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بیان کتبی | مرتب‌سازی اطلاعات | درک کتبی</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بیان کتبی | ترتیب‌دهی اطلاعات | درک کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>صندوق‌داران | کارشناسان خدمات پس از فروش و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | رانندگان توزیع و پخش کالا | فروشندگان خرده‌فروشی | کارگران انبار و چیدمان کالا | کارشناسان بازاریابی تلفنی</t>
+          <t>صندوق‌داران | کارشناسان خدمات و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | رانندگان توزیع و فروش مویرگی | فروشندگان خرده‌فروشی | متصدیان چیدمان و آماده‌سازی سفارش | کارشناسان بازاریابی تلفنی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>بازاریابی و فروش | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | اقتصاد و حسابداری | رایانه و الکترونیک | علوم ارتباطات و رسانه</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | مدیریت و اداره | اقتصاد و حسابداری | رایانه و الکترونیک | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>فروشندگان خرده‌فروشی | کارشناسان فروش خدمات به‌جز تبلیغات، بیمه، مالی و گردشگری | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و تولیدی محصولات فنی و علمی | کارشناسان فروش بیمه | مهندسان فروش | کارشناسان بازاریابی تلفنی</t>
+          <t>فروشندگان خرده‌فروشی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | نمایندگان و کارشناسان فروش بیمه | مهندسان فروش | کارشناسان بازاریابی تلفنی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
